--- a/data/credit_bond_all_2026-09-10.xlsx
+++ b/data/credit_bond_all_2026-09-10.xlsx
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.78</v>
+        <v>3.7857</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>12.83</v>
@@ -6436,7 +6436,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26中铁十局MTN001</t>
+          <t>26津渤海MTN013</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6446,49 +6446,49 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683587.IB</t>
+          <t>102683603.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.90 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>61.74</v>
+        <v>89.79</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25中铁十局MTN001</t>
+          <t>26津渤海MTN012</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.12Y+N</t>
+          <t>1.96Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.0901</t>
+          <t>2.2654</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中铁十局集团有限公司</t>
+          <t>天津渤海国有资产经营管理有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 28.52</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6527,15 +6527,19 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W28" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>2.16%~2.26%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6543,24 +6547,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限14亿元,拟用于偿还发行人有息债务。</t>
+          <t>本期中期票据本期发行采用发行金额动态调整机制，基础发行金额0.00亿元，发行金额上限4.00亿元，拟用于偿还发行人本部到期债务融资工具本金。[24津渤海MTN008]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中铁十局集团有限公司2026年度第一期中期票据</t>
+          <t>天津渤海国有资产经营管理有限公司2026年度第十三期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2028-09-11</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6617,27 +6617,27 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY28" s="3" t="inlineStr">
@@ -6665,12 +6665,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ28" s="3"/>
+      <c r="AZ28" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26津渤海MTN013</t>
+          <t>26中铁十局MTN001</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6680,64 +6682,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102683603.IB</t>
+          <t>102683587.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.50</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>89.79</v>
+        <v>61.74</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26津渤海MTN012</t>
+          <t>25中铁十局MTN001</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>1.96Y</t>
+          <t>4.12Y+N</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.2654</t>
+          <t>2.0901</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>2.2400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>天津渤海国有资产经营管理有限公司</t>
+          <t>中铁十局集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 28.52</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6747,7 +6749,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6761,19 +6763,15 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+        <v>1.19</v>
+      </c>
+      <c r="W29" s="3"/>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.16%~2.26%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6781,20 +6779,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z29" s="3"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据本期发行采用发行金额动态调整机制，基础发行金额0.00亿元，发行金额上限4.00亿元，拟用于偿还发行人本部到期债务融资工具本金。[24津渤海MTN008]</t>
+          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限14亿元,拟用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,国投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6805,7 +6807,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6815,7 +6817,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>天津渤海国有资产经营管理有限公司2026年度第十三期中期票据</t>
+          <t>中铁十局集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6825,7 +6827,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2028-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6851,27 +6853,27 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6886,12 +6888,12 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY29" s="3" t="inlineStr">
@@ -6899,9 +6901,7 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ29" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ29" s="3"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
@@ -13467,7 +13467,7 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>1.13</v>
+        <v>1.1333</v>
       </c>
       <c r="V58" s="4" t="n">
         <v>1.09</v>
@@ -15926,7 +15926,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26云能MTN005</t>
+          <t>26太仓水务MTN003</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -15936,64 +15936,64 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>102683589.IB</t>
+          <t>102683598.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>52.74</v>
+        <v>52.94</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>26云能MTN004</t>
+          <t>24太仓水务MTN002</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>4.86Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>2.0841</t>
+          <t>1.7376</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>太仓市水务集团有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.63</t>
+          <t>C- 11.53</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>2.5</v>
+        <v>13.0</v>
       </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
@@ -16029,28 +16029,28 @@
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元，公司拟将募集资金扣除发行费用后全部用于偿还有息债务[24云能投MTN011]</t>
+          <t>本期中期票据募集资金2亿元，发行人计划将募集资金全部用于偿还到期的有息负债。</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年度第五期中期票据</t>
+          <t>太仓市水务集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
@@ -16102,34 +16102,34 @@
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR69" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AS69" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AT69" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU69" s="3" t="inlineStr">
         <is>
           <t/>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX69" s="3" t="inlineStr">
@@ -16156,13 +16156,13 @@
         </is>
       </c>
       <c r="AZ69" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26太仓水务MTN003</t>
+          <t>26中铝集MTN004(科创债)</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16172,64 +16172,64 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>102683598.IB</t>
+          <t>102683597.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>52.94</v>
+        <v>18.74</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>24太仓水务MTN002</t>
+          <t>26中铝集MTN003(科创债)</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.7376</t>
+          <t>1.7470</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>太仓市水务集团有限公司</t>
+          <t>中国铝业集团有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C- 11.53</t>
+          <t>C 28.64</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16253,40 +16253,40 @@
         </is>
       </c>
       <c r="U70" s="4" t="n">
-        <v>5.8</v>
+        <v>2.64</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>13.0</v>
+        <v>1.38</v>
       </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金2亿元，发行人计划将募集资金全部用于偿还到期的有息负债。</t>
+          <t>发行人本期科技创新债券募集资金5亿元,用于偿还发行人本部有息债务。</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="AF70" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG70" s="3" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>太仓市水务集团有限公司2026年度第三期中期票据</t>
+          <t>中国铝业集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK70" s="3"/>
@@ -16338,32 +16338,32 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="AW70" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX70" s="3" t="inlineStr">
@@ -16391,14 +16391,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ70" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ70" s="3"/>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26中铝集MTN004(科创债)</t>
+          <t>26宿州城投MTN004</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16408,19 +16406,19 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102683597.IB</t>
+          <t>102683590.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>5.0</v>
+        <v>6.08</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>5.0</v>
+        <v>6.08</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -16428,44 +16426,44 @@
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>18.74</v>
+        <v>48.94</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26中铝集MTN003(科创债)</t>
+          <t>26宿州城投MTN003</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.7470</t>
+          <t>1.7307</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>1.7600/1.6900</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>中国铝业集团有限公司</t>
+          <t>宿州市城市建设投资集团(控股)有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C 28.64</t>
+          <t>C- 23.11</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16475,7 +16473,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 10:00</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -16489,40 +16487,40 @@
         </is>
       </c>
       <c r="U71" s="4" t="n">
-        <v>2.64</v>
+        <v>4.3977</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>安徽省-宿州市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券募集资金5亿元,用于偿还发行人本部有息债务。</t>
+          <t>本次中期票据发行金额6.08亿元人民币,募集资金全部用于归还发行人债务融资工具。[25宿州城投CP003]</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
@@ -16533,7 +16531,7 @@
       </c>
       <c r="AF71" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG71" s="3" t="inlineStr">
@@ -16543,7 +16541,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>中国铝业集团有限公司2026年度第四期科技创新债券</t>
+          <t>宿州市城市建设投资集团(控股)有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16553,7 +16551,7 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
@@ -16574,32 +16572,32 @@
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
@@ -16627,12 +16625,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ71" s="3"/>
+      <c r="AZ71" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26宿州城投MTN004</t>
+          <t>26招商局MTN001</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>102683590.IB</t>
+          <t>102683592.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -16651,55 +16651,55 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>6.08</v>
+        <v>50.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>6.08</v>
+        <v>50.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>48.94</v>
+        <v>29.94</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>26宿州城投MTN003</t>
+          <t>24CMGK01</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>2.77Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.7307</t>
+          <t>1.5510</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.6900</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>宿州市城市建设投资集团(控股)有限公司</t>
+          <t>招商局集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C- 23.11</t>
+          <t>B- 46.42</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>09-10 10:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16723,40 +16723,38 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>1.12</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宿州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额6.08亿元人民币,募集资金全部用于归还发行人债务融资工具。[25宿州城投CP003]</t>
+          <t>公司此次发行50亿元中期票据,募集资金拟用于偿还发行人本部的到期债务。</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
@@ -16767,7 +16765,7 @@
       </c>
       <c r="AF72" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG72" s="3" t="inlineStr">
@@ -16777,7 +16775,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>宿州市城市建设投资集团(控股)有限公司2026年度第四期中期票据</t>
+          <t>招商局集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16808,12 +16806,12 @@
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
@@ -16823,17 +16821,17 @@
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU72" s="3" t="inlineStr">
@@ -16861,14 +16859,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ72" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ72" s="3"/>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26川华西SCP004</t>
+          <t>26吴中城投MTN002</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -16878,64 +16874,64 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>012682228.IB</t>
+          <t>102683594.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.78</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>53.43</v>
+        <v>44.94</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>26川华西SCP003</t>
+          <t>26吴中城投MTN001</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.8046</t>
+          <t>1.7208</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.6994</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>四川华西集团有限公司</t>
+          <t>苏州市吴中城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 36.46</t>
+          <t>C- 17.72</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -16945,7 +16941,7 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -16959,19 +16955,19 @@
         </is>
       </c>
       <c r="U73" s="4" t="n">
-        <v>1.68</v>
+        <v>6.17</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.79%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
@@ -16982,23 +16978,23 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>本期债券计划发行规模为5.00亿元,募集资金扣除承销费后,拟用于偿还发行人到期债务融资工具。[25川华西SCP007]</t>
+          <t>发行人本期债务融资工具发行金额3.00亿元,拟全部用于归还发行人即将到期的债务融资工具本金。[23吴中城投PPN007]</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
@@ -17013,7 +17009,7 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>四川华西集团有限公司2026年度第四期超短期融资券</t>
+          <t>苏州市吴中城市建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -17023,7 +17019,7 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK73" s="3"/>
@@ -17044,7 +17040,7 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
@@ -17054,22 +17050,22 @@
       </c>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -17097,12 +17093,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ73" s="3"/>
+      <c r="AZ73" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26招商局MTN001</t>
+          <t>26凤城河MTN003</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17112,7 +17110,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>102683592.IB</t>
+          <t>102683600.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -17121,55 +17119,55 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>50.0</v>
+        <v>4.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>50.0</v>
+        <v>4.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>29.94</v>
+        <v>48.94</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>24CMGK01</t>
+          <t>26凤城河MTN002</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2.77Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.5510</t>
+          <t>1.7412</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/1.5900</t>
+          <t>1.9000/--</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>招商局集团有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B- 46.42</t>
+          <t>C- 17.90</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17193,38 +17191,40 @@
         </is>
       </c>
       <c r="U74" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="V74" s="3"/>
+        <v>3.15</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>1.52</v>
+      </c>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>公司此次发行50亿元中期票据,募集资金拟用于偿还发行人本部的到期债务。</t>
+          <t>本次中期票据发行金额为4亿元,用于偿还发行人存量债务融资工具[23凤城河MTN004]</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
@@ -17235,7 +17235,7 @@
       </c>
       <c r="AF74" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG74" s="3" t="inlineStr">
@@ -17245,7 +17245,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>招商局集团有限公司2026年度第一期中期票据</t>
+          <t>泰州凤城河建设发展有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17276,32 +17276,32 @@
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
@@ -17334,74 +17334,70 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26吴中城投MTN002</t>
+          <t>26西部证券CP008</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 17:00</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>102683594.IB</t>
+          <t>072610179.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.48Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
+        <v>15.0</v>
+      </c>
+      <c r="G75" s="3"/>
       <c r="H75" s="4" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>44.94</v>
+        <v>30.29</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26吴中城投MTN001</t>
+          <t>26西部证券CP005</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>158D</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.7208</t>
+          <t>1.5147</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>苏州市吴中城市建设投资集团有限公司</t>
+          <t>西部证券股份有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>C- 17.72</t>
+          <t>C+ 33.71</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17411,7 +17407,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -17424,47 +17420,39 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U75" s="4" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>1.67</v>
-      </c>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
-        </is>
-      </c>
-      <c r="AB75" s="3" t="inlineStr">
-        <is>
-          <t>发行人本期债务融资工具发行金额3.00亿元,拟全部用于归还发行人即将到期的债务融资工具本金。[23吴中城投PPN007]</t>
-        </is>
-      </c>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="AB75" s="3"/>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,南京银行股份有限公司</t>
+          <t>西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
@@ -17479,7 +17467,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>苏州市吴中城市建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>西部证券股份有限公司2026年度第八期短期融资券</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17489,7 +17477,7 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
@@ -17500,7 +17488,7 @@
       </c>
       <c r="AM75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN75" s="3" t="inlineStr">
@@ -17510,32 +17498,32 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17563,14 +17551,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ75" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ75" s="3"/>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN003</t>
+          <t>26海江投资MTN003</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17580,30 +17566,30 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>102683600.IB</t>
+          <t>102683596.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>4.0</v>
+        <v>5.5</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>4.0</v>
+        <v>5.5</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>48.94</v>
+        <v>27.74</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -17612,32 +17598,32 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN002</t>
+          <t>26海江投资MTN002</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>2.60Y+2.00Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.7412</t>
+          <t>1.6979</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.9000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>宁波市镇海区海江投资发展有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C- 17.90</t>
+          <t>C- 19.28</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17661,19 +17647,19 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>3.15</v>
+        <v>5.13</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -17684,17 +17670,17 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为4亿元,用于偿还发行人存量债务融资工具[23凤城河MTN004]</t>
+          <t>本期发行5.5亿元中期票据,募集资金全部用于偿还发行人的债务融资工具的本金[21海江投资MTN002]</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>宁波银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
@@ -17715,7 +17701,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第三期中期票据</t>
+          <t>宁波市镇海区海江投资发展有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17725,7 +17711,7 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK76" s="3"/>
@@ -17746,27 +17732,27 @@
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
@@ -17776,7 +17762,7 @@
       </c>
       <c r="AU76" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV76" s="3" t="inlineStr">
@@ -17786,7 +17772,7 @@
       </c>
       <c r="AW76" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX76" s="3" t="inlineStr">
@@ -17804,70 +17790,74 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26西部证券CP008</t>
+          <t>26张家城投MTN006</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>09-10 17:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>072610179.IB</t>
+          <t>102683595.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>0.48Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>15.0</v>
+        <v>1.6</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G77" s="3"/>
+        <v>1.6</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.30</t>
+        </is>
+      </c>
       <c r="H77" s="4" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>30.29</v>
+        <v>55.44</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>26西部证券CP005</t>
+          <t>26张家城投MTN004</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>158D</t>
+          <t>6.82Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1.5147</t>
+          <t>2.0558</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0800/--</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
+          <t>张家港市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.71</t>
+          <t>C- 20.37</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -17890,39 +17880,47 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
+      <c r="U77" s="4" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="V77" s="4" t="n">
+        <v>2.67</v>
+      </c>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="AB77" s="3"/>
+          <t>江苏省-苏州市</t>
+        </is>
+      </c>
+      <c r="AB77" s="3" t="inlineStr">
+        <is>
+          <t>本期发行金额1.6亿元,拟全部用于偿还本部债务融资工具本金。[26张家城投SCP001,21张家城投MTN004]</t>
+        </is>
+      </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
+          <t>中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
       <c r="AE77" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF77" s="3" t="inlineStr">
@@ -17937,7 +17935,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司2026年度第八期短期融资券</t>
+          <t>张家港市城市投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -17947,10 +17945,14 @@
       </c>
       <c r="AJ77" s="3" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
-        </is>
-      </c>
-      <c r="AK77" s="3"/>
+          <t>2033-09-11</t>
+        </is>
+      </c>
+      <c r="AK77" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL77" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -17958,42 +17960,42 @@
       </c>
       <c r="AM77" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN77" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AN77" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO77" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -18026,7 +18028,7 @@
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26海江投资MTN003</t>
+          <t>26鄂联投MTN002</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -18036,64 +18038,64 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>102683596.IB</t>
+          <t>102690028.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>5.5</v>
+        <v>8.0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>5.5</v>
+        <v>8.0</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>27.74</v>
+        <v>54.94</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>26海江投资MTN002</t>
+          <t>26联投Y4</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2.60Y+2.00Y</t>
+          <t>2.80Y+N</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.6979</t>
+          <t>1.8123</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>宁波市镇海区海江投资发展有限公司</t>
+          <t>湖北省联合发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C- 19.28</t>
+          <t>B- 36.56</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18103,7 +18105,7 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -18117,40 +18119,40 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>5.13</v>
+        <v>2.775</v>
       </c>
       <c r="V78" s="4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>本期发行5.5亿元中期票据,募集资金全部用于偿还发行人的债务融资工具的本金[21海江投资MTN002]</t>
+          <t>本期中期票据发行金额为8亿元,募集资金拟全部用于偿还发行人非金融企业债务融资工具本金[23鄂联投MTN004]</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,交通银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
@@ -18171,7 +18173,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>宁波市镇海区海江投资发展有限公司2026年度第三期中期票据</t>
+          <t>湖北省联合发展投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -18181,7 +18183,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK78" s="3"/>
@@ -18202,12 +18204,12 @@
       </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
@@ -18232,7 +18234,7 @@
       </c>
       <c r="AU78" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV78" s="3" t="inlineStr">
@@ -18242,7 +18244,7 @@
       </c>
       <c r="AW78" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX78" s="3" t="inlineStr">
@@ -18255,12 +18257,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ78" s="3"/>
+      <c r="AZ78" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN006</t>
+          <t>26华电新能MTN001</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18270,64 +18274,64 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>102683595.IB</t>
+          <t>102683601.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1.6</v>
+        <v>15.0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1.6</v>
+        <v>15.0</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>55.44</v>
+        <v>27.74</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN004</t>
+          <t>G26HX2</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>6.82Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>2.0558</t>
+          <t>1.7418</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>2.0800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司</t>
+          <t>华电新能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C- 20.37</t>
+          <t>A- 63.76</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18337,7 +18341,7 @@
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 10:00</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -18351,40 +18355,40 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>2.125</v>
+        <v>2.4667</v>
       </c>
       <c r="V79" s="4" t="n">
-        <v>2.67</v>
+        <v>1.02</v>
       </c>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额1.6亿元,拟全部用于偿还本部债务融资工具本金。[26张家城投SCP001,21张家城投MTN004]</t>
+          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
@@ -18395,7 +18399,7 @@
       </c>
       <c r="AF79" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG79" s="3" t="inlineStr">
@@ -18405,7 +18409,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>华电新能源集团股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18415,14 +18419,10 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2033-09-11</t>
-        </is>
-      </c>
-      <c r="AK79" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK79" s="3"/>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -18440,32 +18440,32 @@
       </c>
       <c r="AO79" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18498,7 +18498,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26鄂联投MTN002</t>
+          <t>26苏州港MTN003(并购)</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18508,64 +18508,64 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>102690028.IB</t>
+          <t>102683599.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>8.0</v>
+        <v>1.5</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>8.0</v>
+        <v>1.5</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>54.94</v>
+        <v>46.94</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26联投Y4</t>
+          <t>26苏州港MTN001</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2.80Y+N</t>
+          <t>2.68Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.8123</t>
+          <t>1.7252</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司</t>
+          <t>江苏苏州港集团有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>B- 36.56</t>
+          <t>C- 15.25</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -18589,19 +18589,17 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>2.775</v>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>1.08</v>
-      </c>
+        <v>2.93</v>
+      </c>
+      <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18612,17 +18610,17 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为8亿元,募集资金拟全部用于偿还发行人非金融企业债务融资工具本金[23鄂联投MTN004]</t>
+          <t>本次中期票据本期发行金额1.5亿元,其中0.72亿元用于偿还发行人本部及下属子公司的有息负债,0.78亿元用于并购用途,支付对子公司太仓鑫海港口开发有限公司增资款项。</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信银行股份有限公司</t>
+          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
@@ -18643,7 +18641,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司2026年度第二期中期票据</t>
+          <t>江苏苏州港集团有限公司2026年度第三期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18674,32 +18672,32 @@
       </c>
       <c r="AO80" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18714,7 +18712,7 @@
       </c>
       <c r="AW80" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX80" s="3" t="inlineStr">
@@ -18727,14 +18725,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ80" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ80" s="3"/>
     </row>
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26华电新能MTN001</t>
+          <t>26南昌轨交MTN005(绿色)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18744,64 +18740,64 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>102683601.IB</t>
+          <t>102683576.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>2.00 ~ 2.18</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>27.74</v>
+        <v>50.03</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>G26HX2</t>
+          <t>26南昌轨交MTN004(绿色)</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>4.65Y</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.7418</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司</t>
+          <t>南昌轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>A- 63.76</t>
+          <t>C 29.41</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18811,7 +18807,7 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>09-10 10:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -18825,19 +18821,19 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>2.4667</v>
+        <v>1.4</v>
       </c>
       <c r="V81" s="4" t="n">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -18848,17 +18844,17 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
+          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
@@ -18869,7 +18865,7 @@
       </c>
       <c r="AF81" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG81" s="3" t="inlineStr">
@@ -18879,7 +18875,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司2026年度第一期中期票据</t>
+          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -18889,7 +18885,7 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK81" s="3"/>
@@ -18910,32 +18906,32 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -18963,22 +18959,24 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ81" s="3"/>
+      <c r="AZ81" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26长春城投MTN001</t>
+          <t>26淮国02</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>102683602.IB</t>
+          <t>283955.SH</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -18987,55 +18985,55 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>10.0</v>
+        <v>3.91</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>10.0</v>
+        <v>3.91</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>62.94</v>
+        <v>46.94</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>25长春城投MTN001A</t>
+          <t>26淮国01</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>3.78Y+5.00Y</t>
+          <t>2.62Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>2.0296</t>
+          <t>1.7220</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/1.6900</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>长春城投建设投资(集团)有限公司</t>
+          <t>淮安国发投资集团有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C- 10.66</t>
+          <t>B- 35.63</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19059,21 +19057,15 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>1.72</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X82" s="3" t="inlineStr">
-        <is>
-          <t>2.01%~2.11%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X82" s="3"/>
       <c r="Y82" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -19082,23 +19074,23 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行金额人民币0亿元,本期发行金额上限人民币10亿元(含10亿元),募集资金全部用于偿还发行人债务融资工具本金。[23长春城投MTN003]</t>
+          <t>本期公司债券募集资金3.91亿元,扣除发行费用后,拟用于偿还子公司到期公司债券本金[25淮高01]</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,浙商证券股份有限公司</t>
+          <t>东吴证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF82" s="3" t="inlineStr">
@@ -19108,17 +19100,17 @@
       </c>
       <c r="AG82" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>长春城投建设投资(集团)有限公司2026年度第一期中期票据</t>
+          <t>淮安国发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ82" s="3" t="inlineStr">
@@ -19129,12 +19121,12 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AM82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN82" s="3" t="inlineStr">
@@ -19144,7 +19136,7 @@
       </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP82" s="3" t="inlineStr">
@@ -19154,22 +19146,22 @@
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>园林工程</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19197,81 +19189,79 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ82" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ82" s="3"/>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26苏州港MTN003(并购)</t>
+          <t>26延安01</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>102683599.IB</t>
+          <t>283970.SH</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>1.5</v>
+        <v>9.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1.5</v>
+        <v>9.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>46.94</v>
+        <v>76.74</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>26苏州港MTN001</t>
+          <t>24延安04</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>2.68Y</t>
+          <t>5.25Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.7252</t>
+          <t>2.0543</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>江苏苏州港集团有限公司</t>
+          <t>延安城市建设投资(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>C- 15.25</t>
+          <t>C- 23.74</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19281,7 +19271,7 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -19295,44 +19285,48 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>2.93</v>
+        <v>3.29</v>
       </c>
       <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.23%~2.33%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z83" s="3"/>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>陕西省-延安市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据本期发行金额1.5亿元,其中0.72亿元用于偿还发行人本部及下属子公司的有息负债,0.78亿元用于并购用途,支付对子公司太仓鑫海港口开发有限公司增资款项。</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期的公司债券本金[23延安04,23延安05]</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD83" s="3"/>
+          <t>东兴证券股份有限公司,国投证券股份有限公司,西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD83" s="3" t="inlineStr">
+        <is>
+          <t>延安公用事业发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE83" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF83" s="3" t="inlineStr">
@@ -19342,28 +19336,28 @@
       </c>
       <c r="AG83" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>江苏苏州港集团有限公司2026年度第三期中期票据(并购)</t>
+          <t>延安城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK83" s="3"/>
       <c r="AL83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AM83" s="3" t="inlineStr">
@@ -19378,32 +19372,32 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
@@ -19413,7 +19407,7 @@
       </c>
       <c r="AV83" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW83" s="3" t="inlineStr">
@@ -19436,7 +19430,7 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN005(绿色)</t>
+          <t>26江津华信PPN003</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19446,64 +19440,64 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>102683576.IB</t>
+          <t>032690019.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>10.0</v>
+        <v>4.72</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>10.0</v>
+        <v>4.72</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.18</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>50.03</v>
+        <v>52.94</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN004(绿色)</t>
+          <t>24江津04</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>4.65Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.7690</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>C 29.41</t>
+          <t>C 27.64</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19527,46 +19521,46 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>1.4</v>
+        <v>4.4703</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>1.82</v>
+        <v>55.0</v>
       </c>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z84" s="3"/>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
+          <t>发行人本期定向债务融资工具募集资金4.72亿元拟全部用于偿还有息债务[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司,长江证券股份有限公司,长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
       <c r="AE84" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF84" s="3" t="inlineStr">
@@ -19581,17 +19575,17 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK84" s="3"/>
@@ -19627,17 +19621,17 @@
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19666,80 +19660,80 @@
         </is>
       </c>
       <c r="AZ84" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26淮国02</t>
+          <t>26许昌投资PPN004</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>283955.SH</t>
+          <t>032680521.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>3.91</v>
+        <v>8.97</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>3.91</v>
+        <v>8.97</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>46.94</v>
+        <v>50.03</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>26淮国01</t>
+          <t>26许昌投资PPN005</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>2.62Y</t>
+          <t>4.92Y+5.00Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.7220</t>
+          <t>2.1614</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>1.7700/1.6900</t>
+          <t>--/2.1500</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>淮安国发投资集团有限公司</t>
+          <t>许昌市投资集团有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>B- 35.63</t>
+          <t>B- 39.59</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19749,7 +19743,7 @@
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
@@ -19763,40 +19757,46 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V85" s="3"/>
+        <v>2.631</v>
+      </c>
+      <c r="V85" s="4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X85" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X85" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>河南省-许昌市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金3.91亿元,扣除发行费用后,拟用于偿还子公司到期公司债券本金[25淮高01]</t>
+          <t>本期发行金额为8.97亿元,用于偿还发行人本部到期债务融资工具本金。[21许昌投资MTN001,21许昌投资PPN001]</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD85" s="3"/>
       <c r="AE85" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF85" s="3" t="inlineStr">
@@ -19806,12 +19806,12 @@
       </c>
       <c r="AG85" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>淮安国发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>许昌市投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19821,86 +19821,88 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK85" s="3"/>
       <c r="AL85" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM85" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO85" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP85" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ85" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR85" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS85" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT85" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU85" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AV85" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW85" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX85" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY85" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AN85" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO85" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP85" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ85" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR85" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS85" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT85" s="3" t="inlineStr">
-        <is>
-          <t>园林工程</t>
-        </is>
-      </c>
-      <c r="AU85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV85" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW85" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX85" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY85" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AZ85" s="3"/>
+      <c r="AZ85" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26延安01</t>
+          <t>26宿新02</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -19910,64 +19912,64 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>283970.SH</t>
+          <t>283917.SH</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>76.74</v>
+        <v>49.94</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>24延安04</t>
+          <t>26宿新01</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>5.25Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>2.0543</t>
+          <t>1.7309</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>延安城市建设投资(集团)有限责任公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C- 23.74</t>
+          <t>B- 37.34</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -19977,7 +19979,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -19991,19 +19993,15 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>3.29</v>
+        <v>5.5</v>
       </c>
       <c r="V86" s="3"/>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X86" s="3" t="inlineStr">
-        <is>
-          <t>2.23%~2.33%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X86" s="3"/>
       <c r="Y86" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -20012,24 +20010,20 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>陕西省-延安市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期的公司债券本金[23延安04,23延安05]</t>
+          <t>本期公司债券募集资金5亿元扣除发行费用后,拟全部用于偿还到期公司债券本金。[23宿控01]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,国投证券股份有限公司,西部证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD86" s="3" t="inlineStr">
-        <is>
-          <t>延安公用事业发展集团有限公司</t>
-        </is>
-      </c>
+          <t>长江证券股份有限公司,财信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,万联证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD86" s="3"/>
       <c r="AE86" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -20047,7 +20041,7 @@
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>延安城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>宿迁市新城控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
@@ -20057,7 +20051,7 @@
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK86" s="3"/>
@@ -20068,7 +20062,7 @@
       </c>
       <c r="AM86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN86" s="3" t="inlineStr">
@@ -20078,32 +20072,32 @@
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
@@ -20113,7 +20107,7 @@
       </c>
       <c r="AV86" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW86" s="3" t="inlineStr">
@@ -20136,7 +20130,7 @@
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26江津华信PPN003</t>
+          <t>26川华西SCP004</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20146,49 +20140,49 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>032690019.IB</t>
+          <t>012682228.IB</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>4.72</v>
+        <v>5.0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>4.72</v>
+        <v>5.0</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 1.78</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>52.94</v>
+        <v>53.43</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>24江津04</t>
+          <t>26川华西SCP003</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>1.7690</t>
+          <t>1.8046</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -20198,12 +20192,12 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>四川华西集团有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C 27.64</t>
+          <t>B- 36.46</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20227,19 +20221,19 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>4.4703</v>
+        <v>1.68</v>
       </c>
       <c r="V87" s="4" t="n">
-        <v>55.0</v>
+        <v>1.11</v>
       </c>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.75%~1.79%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
@@ -20250,23 +20244,23 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具募集资金4.72亿元拟全部用于偿还有息债务[25江津华信CP003]</t>
+          <t>本期债券计划发行规模为5.00亿元,募集资金扣除承销费后,拟用于偿还发行人到期债务融资工具。[25川华西SCP007]</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司,长江证券股份有限公司,长城证券股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD87" s="3"/>
       <c r="AE87" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF87" s="3" t="inlineStr">
@@ -20281,17 +20275,17 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第三期定向债务融资工具</t>
+          <t>四川华西集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-06-08</t>
         </is>
       </c>
       <c r="AK87" s="3"/>
@@ -20312,32 +20306,32 @@
       </c>
       <c r="AO87" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP87" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR87" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS87" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT87" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU87" s="3" t="inlineStr">
@@ -20365,14 +20359,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ87" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ87" s="3"/>
     </row>
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26许昌投资PPN004</t>
+          <t>26长春城投MTN001</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20382,64 +20374,64 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>032680521.IB</t>
+          <t>102683602.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>8.97</v>
+        <v>10.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>8.97</v>
+        <v>10.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>50.03</v>
+        <v>62.94</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>26许昌投资PPN005</t>
+          <t>25长春城投MTN001A</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+5.00Y</t>
+          <t>3.78Y+5.00Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>2.1614</t>
+          <t>2.0296</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>--/2.1500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>许昌市投资集团有限公司</t>
+          <t>长春城投建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>B- 39.59</t>
+          <t>C- 10.66</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20449,7 +20441,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -20463,46 +20455,46 @@
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>2.631</v>
+        <v>4.93</v>
       </c>
       <c r="V88" s="4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>河南省-许昌市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为8.97亿元,用于偿还发行人本部到期债务融资工具本金。[21许昌投资MTN001,21许昌投资PPN001]</t>
+          <t>本期基础发行金额人民币0亿元,本期发行金额上限人民币10亿元(含10亿元),募集资金全部用于偿还发行人债务融资工具本金。[23长春城投MTN003]</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF88" s="3" t="inlineStr">
@@ -20517,17 +20509,17 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>许昌市投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>长春城投建设投资(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK88" s="3"/>
@@ -20553,22 +20545,22 @@
       </c>
       <c r="AP88" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ88" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR88" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS88" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT88" s="3" t="inlineStr">
@@ -20578,7 +20570,7 @@
       </c>
       <c r="AU88" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV88" s="3" t="inlineStr">
@@ -20588,7 +20580,7 @@
       </c>
       <c r="AW88" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX88" s="3" t="inlineStr">
@@ -20608,59 +20600,59 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26宿新02</t>
+          <t>26云能MTN005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>283917.SH</t>
+          <t>102683589.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>49.94</v>
+        <v>52.74</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>26宿新01</t>
+          <t>26云能MTN004</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.86Y</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.7309</t>
+          <t>2.0841</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -20670,12 +20662,12 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>B- 37.34</t>
+          <t>C+ 34.63</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20685,7 +20677,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -20699,40 +20691,46 @@
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V89" s="3"/>
+        <v>4.41</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W89" s="3" t="inlineStr">
         <is>
           <t>6+</t>
         </is>
       </c>
-      <c r="X89" s="3"/>
+      <c r="X89" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y89" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金5亿元扣除发行费用后,拟全部用于偿还到期公司债券本金。[23宿控01]</t>
+          <t>本期中期票据发行规模10亿元，公司拟将募集资金扣除发行费用后全部用于偿还有息债务[24云能投MTN011]</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,财信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,万联证券股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
       <c r="AE89" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF89" s="3" t="inlineStr">
@@ -20742,96 +20740,98 @@
       </c>
       <c r="AG89" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>云南省能源集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK89" s="3"/>
       <c r="AL89" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO89" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP89" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ89" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR89" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS89" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT89" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU89" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM89" s="3" t="inlineStr">
+      <c r="AV89" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW89" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX89" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY89" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AN89" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO89" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP89" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ89" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR89" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS89" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT89" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU89" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV89" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW89" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX89" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY89" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AZ89" s="3"/>
+      <c r="AZ89" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-10.xlsx
+++ b/data/credit_bond_all_2026-09-10.xlsx
@@ -7010,29 +7010,29 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26中铁十局MTN001</t>
+          <t>26肥产01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683587.IB</t>
+          <t>283954.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>14.0</v>
+        <v>6.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>14.0</v>
+        <v>6.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -7040,29 +7040,29 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>61.74</v>
+        <v>92.74</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25中铁十局MTN001</t>
+          <t>26肥产K1</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.12Y+N</t>
+          <t>4.52Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.0901</t>
+          <t>2.2531</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中铁十局集团有限公司</t>
+          <t>肥城市建投产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 29.17</t>
+          <t>B- 39.84</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7097,121 +7097,127 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W30" s="3"/>
+        <v>3.5167</v>
+      </c>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>2.60%~2.70%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>山东省-泰安市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限14亿元,拟用于偿还发行人有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD30" s="3"/>
+          <t>华创证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
+        <is>
+          <t>东北中小企业融资再担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中铁十局集团有限公司2026年度第一期中期票据</t>
+          <t>肥城市建投产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>供热</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>供热</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7221,17 +7227,17 @@
       </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY30" s="3" t="inlineStr">
@@ -7244,59 +7250,59 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26绿城水务MTN003</t>
+          <t>26常山01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102683591.IB</t>
+          <t>283943.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.05</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>45.74</v>
+        <v>46.74</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26绿城水务MTN002</t>
+          <t>24常山01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.68Y</t>
+          <t>137D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2.0101</t>
+          <t>1.5483</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7306,12 +7312,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>广西绿城水务集团股份有限公司</t>
+          <t>常山县城市投资集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>D 4.48</t>
+          <t>C- 15.73</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7335,46 +7341,44 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>3.13</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>浙江省-衢州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>发行人拟发行金额为5亿元，募集资金中，4亿元用于偿还发行人本部债务融资工具本金，1亿元用于偿还发行人有息债务。[23绿城水务MTN003 ]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23常山01]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,兴业银行股份有限公司</t>
+          <t>浙商证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7384,17 +7388,17 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>广西绿城水务集团股份有限公司2026年度第三期中期票据</t>
+          <t>常山县城市投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
@@ -7405,12 +7409,12 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7420,7 +7424,7 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
@@ -7430,27 +7434,27 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7460,7 +7464,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7473,14 +7477,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ31" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ31" s="3"/>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26深圳国际MTN004A(取消发行)</t>
+          <t>26中铁十局MTN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7490,58 +7492,64 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>DY102683582.IB</t>
+          <t>102683587.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>14.0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>14.0</v>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>61.74</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26深圳国控MTN003</t>
+          <t>25中铁十局MTN001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>4.12Y+N</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7449</t>
+          <t>2.0901</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.7450</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>深圳国际控股有限公司</t>
+          <t>中铁十局集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.09</t>
+          <t>C 29.17</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7551,7 +7559,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7564,12 +7572,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="U32" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.19</v>
+      </c>
       <c r="W32" s="3"/>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7577,16 +7589,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期中票发行规模上限为人民币10亿元,拟全部用于偿还发行人即将到期的境内有息债务本息[23国际P7]</t>
+          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限14亿元,拟用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7597,7 +7617,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7607,7 +7627,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>深圳国际控股有限公司2026年度第四期中期票据(品种一)(取消发行)</t>
+          <t>中铁十局集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7643,27 +7663,27 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7678,12 +7698,12 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7696,134 +7716,152 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>润禾转02</t>
+          <t>26绿城水务MTN003</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>09-10 18:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>102683591.IB</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1.65 ~ 2.05</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>26绿城水务MTN002</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>4.68Y</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>2.0101</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>广西绿城水务集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>D 4.48</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
           <t>09-10 15:00</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>123285.SZ</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>6Y</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>-- ~ 100.00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>-127.21</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>宁波润禾高新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>09-10 09:15</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>3.13</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券拟募集资金总额不超过37,000.00万元(含本数),扣除发行费用后,拟投入高端有机硅新材料项目34,000.00万元和补充流动资金3,000.00万元</t>
+          <t>发行人拟发行金额为5亿元，募集资金中，4亿元用于偿还发行人本部债务融资工具本金，1亿元用于偿还发行人有息债务。[23绿城水务MTN003 ]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>2026年宁波润禾高新材料科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>广西绿城水务集团股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7833,60 +7871,60 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2032-09-10</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7907,22 +7945,24 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26肥产01</t>
+          <t>26深圳国际MTN004A(取消发行)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>283954.SH</t>
+          <t>DY102683582.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7931,53 +7971,49 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>92.74</v>
-      </c>
+          <t>1.30 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26肥产K1</t>
+          <t>26深圳国控MTN003</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.52Y</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.2531</t>
+          <t>1.7449</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7450</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>肥城市建投产业投资集团有限公司</t>
+          <t>深圳国际控股有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 39.84</t>
+          <t>C+ 34.09</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7987,7 +8023,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7997,50 +8033,38 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
-      <c r="W34" s="3" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
+      <c r="W34" s="3"/>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.60%~2.70%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
-      <c r="AA34" s="3" t="inlineStr">
-        <is>
-          <t>山东省-泰安市</t>
-        </is>
-      </c>
+      <c r="AA34" s="3"/>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还有息债务</t>
+          <t>本期中票发行规模上限为人民币10亿元,拟全部用于偿还发行人即将到期的境内有息债务本息[23国际P7]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>华创证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>东北中小企业融资再担保股份有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8050,82 +8074,78 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>肥城市建投产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>深圳国际控股有限公司2026年度第四期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>供热</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>供热</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8148,76 +8168,62 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26常山01</t>
+          <t>润禾转02</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>283943.SH</t>
+          <t>123285.SZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>-- ~ 100.00</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.88</v>
+        <v>0.2</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>46.74</v>
+        <v>-127.21</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>24常山01</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>137D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.5483</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.5200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>常山县城市投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>C- 15.73</t>
-        </is>
-      </c>
+          <t>宁波润禾高新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -8225,7 +8231,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:15</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8235,94 +8241,92 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>3.35</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t>1.68%~1.78%</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X35" s="3"/>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z35" s="3"/>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>浙江省-衢州市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23常山01]</t>
+          <t>本次向不特定对象发行可转换公司债券拟募集资金总额不超过37,000.00万元(含本数),扣除发行费用后,拟投入高端有机硅新材料项目34,000.00万元和补充流动资金3,000.00万元</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,天风证券股份有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>常山县城市投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>2026年宁波润禾高新材料科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2032-09-10</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
@@ -8332,27 +8336,27 @@
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -8362,7 +8366,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -12202,7 +12206,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U52" s="3"/>
+      <c r="U52" s="4" t="n">
+        <v>1.28</v>
+      </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-09-10.xlsx
+++ b/data/credit_bond_all_2026-09-10.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-15" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-16" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-15</t>
+          <t>数据来源：DM    2026-09-16</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 22.53</t>
+          <t>C- 22.95</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 39.09</t>
+          <t>B- 38.22</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.24</t>
+          <t>D+ 8.13</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 19.84</t>
+          <t>C- 22.92</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.86</t>
+          <t>D+ 9.21</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 29.90</t>
+          <t>C 29.33</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B 52.56</t>
+          <t>A- 62.38</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 27.86</t>
+          <t>C 26.57</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 19.08</t>
+          <t>C- 19.07</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 44.67</t>
+          <t>A- 70.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4048,7 +4048,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>7.56</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
@@ -4259,7 +4261,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 35.42</t>
+          <t>C+ 34.26</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4495,7 +4497,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 35.42</t>
+          <t>C+ 34.26</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4839,7 +4841,7 @@
       </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4975,7 +4977,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.65</t>
+          <t>C+ 33.83</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5071,7 +5073,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
@@ -5211,7 +5213,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 41.24</t>
+          <t>B- 42.19</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5761,7 +5763,7 @@
       </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5897,7 +5899,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 23.75</t>
+          <t>C- 23.74</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5993,7 +5995,7 @@
       </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -6469,7 +6471,7 @@
       </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6609,7 +6611,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 25.93</t>
+          <t>C 25.89</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6845,7 +6847,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.53</t>
+          <t>C- 13.01</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7077,7 +7079,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 39.84</t>
+          <t>C 27.06</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7177,7 +7179,7 @@
       </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7307,7 +7309,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5200</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -7549,7 +7551,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C 29.17</t>
+          <t>B- 39.58</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7783,7 +7785,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>D 4.48</t>
+          <t>D 4.71</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -8013,7 +8015,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.09</t>
+          <t>C+ 34.51</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8451,7 +8453,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 16.08</t>
+          <t>C- 23.42</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8923,7 +8925,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.24</t>
+          <t>B- 37.77</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9155,7 +9157,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 21.45</t>
+          <t>C- 21.81</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9251,7 +9253,7 @@
       </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9627,7 +9629,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>A- 61.65</t>
+          <t>A- 63.13</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9723,7 +9725,7 @@
       </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
@@ -9857,7 +9859,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 22.53</t>
+          <t>C- 22.95</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -10091,7 +10093,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 13.79</t>
+          <t>C- 14.66</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10191,7 +10193,7 @@
       </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10331,7 +10333,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 23.86</t>
+          <t>C 29.59</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10557,7 +10559,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>B- 38.85</t>
+          <t>B- 39.75</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10791,7 +10793,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.82</t>
+          <t>C+ 31.36</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -11021,7 +11023,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 23.31</t>
+          <t>C- 22.88</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11247,7 +11249,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.09</t>
+          <t>C+ 34.51</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11709,7 +11711,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B 53.04</t>
+          <t>B 50.34</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -12183,7 +12185,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C 29.33</t>
+          <t>C 27.82</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12415,7 +12417,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 23.66</t>
+          <t>C- 24.93</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12649,7 +12651,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 14.07</t>
+          <t>C- 15.98</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12885,7 +12887,7 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C 28.91</t>
+          <t>C 29.73</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -13355,7 +13357,7 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 18.72</t>
+          <t>C- 16.75</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13591,7 +13593,7 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C- 20.37</t>
+          <t>C- 21.16</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13821,7 +13823,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.30</t>
+          <t>B- 36.86</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -14047,7 +14049,7 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 20.08</t>
+          <t>C- 19.83</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14218,7 +14220,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26鄂联投MTN002</t>
+          <t>26苏州港MTN003(并购)</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14228,64 +14230,64 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>102690028.IB</t>
+          <t>102683599.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>8.0</v>
+        <v>1.5</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>8.0</v>
+        <v>1.5</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>54.94</v>
+        <v>46.94</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26联投Y4</t>
+          <t>26苏州港MTN001</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2.80Y+N</t>
+          <t>2.68Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.8123</t>
+          <t>1.7252</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司</t>
+          <t>江苏苏州港集团有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>B- 35.31</t>
+          <t>C- 17.49</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14295,7 +14297,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -14309,19 +14311,17 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>2.775</v>
-      </c>
-      <c r="V61" s="4" t="n">
-        <v>1.08</v>
-      </c>
+        <v>2.9333</v>
+      </c>
+      <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -14332,17 +14332,17 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为8亿元,募集资金拟全部用于偿还发行人非金融企业债务融资工具本金[23鄂联投MTN004]</t>
+          <t>本次中期票据本期发行金额1.5亿元,其中0.72亿元用于偿还发行人本部及下属子公司的有息负债,0.78亿元用于并购用途,支付对子公司太仓鑫海港口开发有限公司增资款项。</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信银行股份有限公司</t>
+          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司2026年度第二期中期票据</t>
+          <t>江苏苏州港集团有限公司2026年度第三期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14394,32 +14394,32 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
@@ -14447,14 +14447,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ61" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ61" s="3"/>
     </row>
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26苏州港MTN003(并购)</t>
+          <t>26南昌轨交MTN005(绿色)</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14464,64 +14462,64 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>102683599.IB</t>
+          <t>102683576.IB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>2.00 ~ 2.18</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>46.94</v>
+        <v>50.03</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26苏州港MTN001</t>
+          <t>26南昌轨交MTN004(绿色)</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.68Y</t>
+          <t>4.65Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7252</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>江苏苏州港集团有限公司</t>
+          <t>南昌轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 14.18</t>
+          <t>C+ 32.85</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14545,17 +14543,19 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>2.9333</v>
-      </c>
-      <c r="V62" s="3"/>
+        <v>1.4</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>1.82</v>
+      </c>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -14566,17 +14566,17 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据本期发行金额1.5亿元,其中0.72亿元用于偿还发行人本部及下属子公司的有息负债,0.78亿元用于并购用途,支付对子公司太仓鑫海港口开发有限公司增资款项。</t>
+          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14597,7 +14597,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>江苏苏州港集团有限公司2026年度第三期中期票据(并购)</t>
+          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
@@ -14643,17 +14643,17 @@
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14681,79 +14681,81 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ62" s="3"/>
+      <c r="AZ62" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN005(绿色)</t>
+          <t>26淮国02</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>102683576.IB</t>
+          <t>283955.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>10.0</v>
+        <v>3.91</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.0</v>
+        <v>3.91</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.18</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>50.03</v>
+        <v>46.94</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN004(绿色)</t>
+          <t>26淮国01</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>4.65Y</t>
+          <t>2.62Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.7220</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>1.7700/1.6900</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司</t>
+          <t>淮安国发投资集团有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.82</t>
+          <t>B- 35.63</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14763,7 +14765,7 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -14777,21 +14779,15 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V63" s="4" t="n">
-        <v>1.82</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X63" s="3" t="inlineStr">
-        <is>
-          <t>2.21%~2.31%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X63" s="3"/>
       <c r="Y63" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14800,23 +14796,23 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
+          <t>本期公司债券募集资金3.91亿元,扣除发行费用后,拟用于偿还子公司到期公司债券本金[25淮高01]</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
+          <t>东吴证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
@@ -14826,33 +14822,33 @@
       </c>
       <c r="AG63" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据</t>
+          <t>淮安国发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
       <c r="AL63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN63" s="3" t="inlineStr">
@@ -14872,22 +14868,22 @@
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>园林工程</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -14915,14 +14911,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ63" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ63" s="3"/>
     </row>
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26淮国02</t>
+          <t>26延安01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14932,64 +14926,64 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>283955.SH</t>
+          <t>283970.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3.91</v>
+        <v>9.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3.91</v>
+        <v>9.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>46.94</v>
+        <v>76.74</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26淮国01</t>
+          <t>24延安04</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2.62Y</t>
+          <t>5.25Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.7220</t>
+          <t>2.0543</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>1.7700/1.6900</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>淮安国发投资集团有限公司</t>
+          <t>延安城市建设投资(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>B- 35.63</t>
+          <t>C 26.13</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14999,7 +14993,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -15013,37 +15007,45 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X64" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>2.23%~2.33%</t>
+        </is>
+      </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>陕西省-延安市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金3.91亿元,扣除发行费用后,拟用于偿还子公司到期公司债券本金[25淮高01]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期的公司债券本金[23延安04,23延安05]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,招商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD64" s="3"/>
+          <t>东兴证券股份有限公司,国投证券股份有限公司,西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr">
+        <is>
+          <t>延安公用事业发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE64" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -15061,7 +15063,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>淮安国发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>延安城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15071,63 +15073,63 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
       <c r="AL64" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>燃气</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM64" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO64" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ64" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR64" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>园林工程</t>
-        </is>
-      </c>
-      <c r="AU64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV64" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW64" s="3" t="inlineStr">
@@ -15150,74 +15152,74 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26延安01</t>
+          <t>26江津华信PPN003</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>283970.SH</t>
+          <t>032690019.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>9.0</v>
+        <v>4.72</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>9.0</v>
+        <v>4.72</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>76.74</v>
+        <v>52.94</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>24延安04</t>
+          <t>24江津04</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>5.25Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>2.0543</t>
+          <t>1.7690</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>延安城市建设投资(集团)有限责任公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C- 23.74</t>
+          <t>C 25.25</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15227,7 +15229,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -15241,17 +15243,19 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="V65" s="3"/>
+        <v>4.4703</v>
+      </c>
+      <c r="V65" s="4" t="n">
+        <v>55.0</v>
+      </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>2.23%~2.33%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -15262,27 +15266,23 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>陕西省-延安市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期的公司债券本金[23延安04,23延安05]</t>
+          <t>发行人本期定向债务融资工具募集资金4.72亿元拟全部用于偿还有息债务[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,国投证券股份有限公司,西部证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD65" s="3" t="inlineStr">
-        <is>
-          <t>延安公用事业发展集团有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,渤海银行股份有限公司,长江证券股份有限公司,长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="AG65" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>延安城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
@@ -15307,63 +15307,63 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO65" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP65" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ65" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR65" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS65" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT65" s="3" t="inlineStr">
-        <is>
-          <t>燃气</t>
-        </is>
-      </c>
-      <c r="AU65" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV65" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW65" s="3" t="inlineStr">
@@ -15381,12 +15381,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ65" s="3"/>
+      <c r="AZ65" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26江津华信PPN003</t>
+          <t>26许昌投资PPN004</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15396,64 +15398,64 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>032690019.IB</t>
+          <t>032680521.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.72</v>
+        <v>8.97</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>4.72</v>
+        <v>8.97</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>52.94</v>
+        <v>50.03</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>24江津04</t>
+          <t>26许昌投资PPN005</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.92Y+5.00Y</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.7690</t>
+          <t>2.1614</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1500</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>许昌市投资集团有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C 27.64</t>
+          <t>B- 43.16</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15477,19 +15479,19 @@
         </is>
       </c>
       <c r="U66" s="4" t="n">
-        <v>4.4703</v>
+        <v>2.631</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>55.0</v>
+        <v>1.7</v>
       </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
@@ -15500,17 +15502,17 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>河南省-许昌市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具募集资金4.72亿元拟全部用于偿还有息债务[25江津华信CP003]</t>
+          <t>本期发行金额为8.97亿元,用于偿还发行人本部到期债务融资工具本金。[21许昌投资MTN001,21许昌投资PPN001]</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司,长江证券股份有限公司,长城证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
@@ -15531,7 +15533,7 @@
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第三期定向债务融资工具</t>
+          <t>许昌市投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15541,7 +15543,7 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK66" s="3"/>
@@ -15562,27 +15564,27 @@
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
@@ -15592,7 +15594,7 @@
       </c>
       <c r="AU66" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AV66" s="3" t="inlineStr">
@@ -15602,7 +15604,7 @@
       </c>
       <c r="AW66" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX66" s="3" t="inlineStr">
@@ -15616,80 +15618,80 @@
         </is>
       </c>
       <c r="AZ66" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26许昌投资PPN004</t>
+          <t>26宿新02</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>032680521.IB</t>
+          <t>283917.SH</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>8.97</v>
+        <v>5.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>8.97</v>
+        <v>5.0</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>50.03</v>
+        <v>49.94</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26许昌投资PPN005</t>
+          <t>26宿新01</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+5.00Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>2.1614</t>
+          <t>1.7309</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/2.1500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>许昌市投资集团有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>B- 43.16</t>
+          <t>B- 37.37</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15699,7 +15701,7 @@
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -15713,21 +15715,15 @@
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>2.631</v>
-      </c>
-      <c r="V67" s="4" t="n">
-        <v>1.7</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X67" s="3" t="inlineStr">
-        <is>
-          <t>2.21%~2.31%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X67" s="3"/>
       <c r="Y67" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -15736,23 +15732,23 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>河南省-许昌市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为8.97亿元,用于偿还发行人本部到期债务融资工具本金。[21许昌投资MTN001,21许昌投资PPN001]</t>
+          <t>本期公司债券募集资金5亿元扣除发行费用后,拟全部用于偿还到期公司债券本金。[23宿控01]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>长江证券股份有限公司,财信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,万联证券股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF67" s="3" t="inlineStr">
@@ -15762,12 +15758,12 @@
       </c>
       <c r="AG67" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>许昌市投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>宿迁市新城控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15777,18 +15773,18 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN67" s="3" t="inlineStr">
@@ -15803,22 +15799,22 @@
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
@@ -15828,7 +15824,7 @@
       </c>
       <c r="AU67" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV67" s="3" t="inlineStr">
@@ -15838,7 +15834,7 @@
       </c>
       <c r="AW67" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX67" s="3" t="inlineStr">
@@ -15851,29 +15847,27 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ67" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ67" s="3"/>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26宿新02</t>
+          <t>26川华西SCP004</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>283917.SH</t>
+          <t>012682228.IB</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -15884,48 +15878,48 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 1.78</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>49.94</v>
+        <v>53.43</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>26宿新01</t>
+          <t>26川华西SCP003</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>1.7309</t>
+          <t>1.8046</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.6994</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>四川华西集团有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>B- 37.34</t>
+          <t>B- 41.15</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15935,7 +15929,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -15949,15 +15943,21 @@
         </is>
       </c>
       <c r="U68" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V68" s="3"/>
+        <v>1.68</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W68" s="3" t="inlineStr">
         <is>
           <t>6+</t>
         </is>
       </c>
-      <c r="X68" s="3"/>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.79%</t>
+        </is>
+      </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -15966,23 +15966,23 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金5亿元扣除发行费用后,拟全部用于偿还到期公司债券本金。[23宿控01]</t>
+          <t>本期债券计划发行规模为5.00亿元,募集资金扣除承销费后,拟用于偿还发行人到期债务融资工具。[25川华西SCP007]</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,财信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,万联证券股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr">
@@ -15992,33 +15992,33 @@
       </c>
       <c r="AG68" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>四川华西集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-06-08</t>
         </is>
       </c>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN68" s="3" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP68" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26川华西SCP004</t>
+          <t>26长春城投MTN001</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -16096,64 +16096,64 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>012682228.IB</t>
+          <t>102683602.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.78</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>53.43</v>
+        <v>62.94</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>26川华西SCP003</t>
+          <t>25长春城投MTN001A</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>3.78Y+5.00Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.8046</t>
+          <t>2.0296</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.6994</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>四川华西集团有限公司</t>
+          <t>长春城投建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>B- 39.32</t>
+          <t>C- 22.80</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -16177,10 +16177,10 @@
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>1.68</v>
+        <v>4.93</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
@@ -16189,34 +16189,34 @@
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.79%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期债券计划发行规模为5.00亿元,募集资金扣除承销费后,拟用于偿还发行人到期债务融资工具。[25川华西SCP007]</t>
+          <t>本期基础发行金额人民币0亿元,本期发行金额上限人民币10亿元(含10亿元),募集资金全部用于偿还发行人债务融资工具本金。[23长春城投MTN003]</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>四川华西集团有限公司2026年度第四期超短期融资券</t>
+          <t>长春城投建设投资(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
@@ -16262,32 +16262,32 @@
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -16315,12 +16315,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ69" s="3"/>
+      <c r="AZ69" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26长春城投MTN001</t>
+          <t>26云能MTN005</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16330,12 +16332,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>102683602.IB</t>
+          <t>102683589.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -16346,33 +16348,33 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>62.94</v>
+        <v>52.74</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>25长春城投MTN001A</t>
+          <t>26云能MTN004</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>3.78Y+5.00Y</t>
+          <t>4.86Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>2.0296</t>
+          <t>2.0841</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -16382,12 +16384,12 @@
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>长春城投建设投资(集团)有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C- 19.22</t>
+          <t>C+ 32.14</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16397,7 +16399,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -16411,10 +16413,10 @@
         </is>
       </c>
       <c r="U70" s="4" t="n">
-        <v>4.93</v>
+        <v>4.41</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
@@ -16423,7 +16425,7 @@
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>2.01%~2.11%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16434,17 +16436,17 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行金额人民币0亿元,本期发行金额上限人民币10亿元(含10亿元),募集资金全部用于偿还发行人债务融资工具本金。[23长春城投MTN003]</t>
+          <t>本期中期票据发行规模10亿元，公司拟将募集资金扣除发行费用后全部用于偿还有息债务[24云能投MTN011]</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,浙商证券股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
@@ -16465,7 +16467,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>长春城投建设投资(集团)有限公司2026年度第一期中期票据</t>
+          <t>云南省能源集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16475,7 +16477,7 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK70" s="3"/>
@@ -16496,32 +16498,32 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16550,13 +16552,13 @@
         </is>
       </c>
       <c r="AZ70" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26云能MTN005</t>
+          <t>26威海银行绿债01</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16566,49 +16568,49 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102683589.IB</t>
+          <t>222680024.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>52.74</v>
+        <v>39.94</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26云能MTN004</t>
+          <t>25威海银行绿色债(柜台)</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>4.86Y</t>
+          <t>2.27Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>2.0841</t>
+          <t>1.6142</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -16618,12 +16620,12 @@
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>威海银行股份有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.56</t>
+          <t>B- 44.21</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16643,23 +16645,19 @@
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="V71" s="4" t="n">
-        <v>2.5</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -16667,26 +16665,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z71" s="3"/>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元，公司拟将募集资金扣除发行费用后全部用于偿还有息债务[24云能投MTN011]</t>
+          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目，同时符合《蓝色金融标准（试用稿）》要求。 </t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
@@ -16701,7 +16703,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年度第五期中期票据</t>
+          <t>威海银行股份有限公司2026年绿色金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16711,53 +16713,53 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
@@ -16785,24 +16787,22 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ71" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ71" s="3"/>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26威海银行绿债01</t>
+          <t>26江南农商行债01</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 16:00</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>222680024.IB</t>
+          <t>212680039.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -16811,55 +16811,55 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>39.94</v>
+        <v>33.94</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>25威海银行绿色债(柜台)</t>
+          <t>24江南农商行债01</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2.27Y</t>
+          <t>1.02Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.6142</t>
+          <t>1.4956</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>威海银行股份有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>B- 39.93</t>
+          <t>B+ 56.94</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16886,12 +16886,12 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
@@ -16899,24 +16899,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z72" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目，同时符合《蓝色金融标准（试用稿）》要求。 </t>
+          <t xml:space="preserve">本期债券募集的资金将用于优化中长期资产负债匹配结构，增加稳定中长期负债来源并支持中长期资产业务的开展。 </t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,国信证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
@@ -16927,7 +16923,7 @@
       </c>
       <c r="AF72" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG72" s="3" t="inlineStr">
@@ -16937,7 +16933,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>威海银行股份有限公司2026年绿色金融债券(第一期)</t>
+          <t>江苏江南农村商业银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16973,7 +16969,7 @@
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
@@ -16988,7 +16984,7 @@
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
@@ -17026,17 +17022,17 @@
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26江南农商行债01</t>
+          <t>26招商局MTN001</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>09-10 16:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>212680039.IB</t>
+          <t>102683592.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -17045,55 +17041,55 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>33.94</v>
+        <v>29.94</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>24江南农商行债01</t>
+          <t>24CMGK01</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>1.02Y</t>
+          <t>2.77Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.4956</t>
+          <t>1.5510</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司</t>
+          <t>招商局集团有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 43.92</t>
+          <t>B+ 59.25</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17113,19 +17109,21 @@
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U73" s="3"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U73" s="4" t="n">
+        <v>1.96</v>
+      </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
@@ -17136,28 +17134,28 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券募集的资金将用于优化中长期资产负债匹配结构，增加稳定中长期负债来源并支持中长期资产业务的开展。 </t>
+          <t>公司此次发行50亿元中期票据,募集资金拟用于偿还发行人本部的到期债务。</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,国信证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG73" s="3" t="inlineStr">
@@ -17167,7 +17165,7 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司2026年金融债券(第一期)</t>
+          <t>招商局集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -17177,53 +17175,53 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK73" s="3"/>
       <c r="AL73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -17256,7 +17254,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26招商局MTN001</t>
+          <t>26农行绿债02BC</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17266,7 +17264,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>102683592.IB</t>
+          <t>222680023.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -17275,55 +17273,55 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>29.94</v>
+        <v>32.94</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>24CMGK01</t>
+          <t>26农业银行绿色债01(柜台)</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2.77Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.5510</t>
+          <t>1.5314</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/1.5900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>招商局集团有限公司</t>
+          <t>中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.04</t>
+          <t>S 90.51</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17343,21 +17341,19 @@
       </c>
       <c r="T74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="n">
-        <v>1.96</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U74" s="3"/>
       <c r="V74" s="3"/>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -17365,7 +17361,11 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z74" s="3"/>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA74" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -17373,18 +17373,18 @@
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>公司此次发行50亿元中期票据,募集资金拟用于偿还发行人本部的到期债务。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,中银国际证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,招商证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
       <c r="AE74" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF74" s="3" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>招商局集团有限公司2026年度第一期中期票据</t>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第二期)(债券通)</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17409,28 +17409,28 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM74" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP74" s="3" t="inlineStr">
@@ -17440,22 +17440,22 @@
       </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
@@ -17488,74 +17488,74 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26农行绿债02BC</t>
+          <t>26深投10</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>222680023.IB</t>
+          <t>525000.SZ</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>80.0</v>
+        <v>5.0</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>32.94</v>
+        <v>40.03</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26农业银行绿色债01(柜台)</t>
+          <t>26深投控MTN004B</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>9.87Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.5314</t>
+          <t>2.1038</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1200/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>S- 89.75</t>
+          <t>C- 23.00</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -17578,16 +17578,18 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U75" s="3"/>
+      <c r="U75" s="4" t="n">
+        <v>6.3</v>
+      </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>2.06%~2.16%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -17602,38 +17604,38 @@
       </c>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,中银国际证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,招商证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
+          <t>国信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司2026年绿色金融债券(第二期)(债券通)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17643,18 +17645,22 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK75" s="3"/>
+          <t>2036-09-14</t>
+        </is>
+      </c>
+      <c r="AK75" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t/>
         </is>
       </c>
       <c r="AM75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN75" s="3" t="inlineStr">
@@ -17664,7 +17670,7 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
@@ -17674,22 +17680,22 @@
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17722,7 +17728,7 @@
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26深投10</t>
+          <t>26深投09</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17732,12 +17738,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>525000.SZ</t>
+          <t>524999.SZ</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -17748,38 +17754,38 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>40.03</v>
+        <v>28.74</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26深投控MTN004B</t>
+          <t>26深投03</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>9.87Y</t>
+          <t>4.78Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>2.1038</t>
+          <t>1.7408</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>2.1200/--</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -17789,7 +17795,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C- 20.47</t>
+          <t>C- 23.00</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17813,7 +17819,7 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>6.3</v>
+        <v>5.48</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3" t="inlineStr">
@@ -17823,7 +17829,7 @@
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>2.06%~2.16%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -17869,7 +17875,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17879,7 +17885,7 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2036-09-14</t>
+          <t>2031-09-14</t>
         </is>
       </c>
       <c r="AK76" s="3" t="inlineStr">
@@ -17962,7 +17968,7 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26深投09</t>
+          <t>26桐乡02</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -17972,64 +17978,64 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>524999.SZ</t>
+          <t>283766.SH</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>28.74</v>
+        <v>30.74</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>26深投03</t>
+          <t>26桐乡01</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>4.78Y</t>
+          <t>2.48Y+2.00Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1.7408</t>
+          <t>1.7291</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>桐乡市城发控股集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C- 20.47</t>
+          <t>C+ 30.97</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18053,17 +18059,17 @@
         </is>
       </c>
       <c r="U77" s="4" t="n">
-        <v>5.48</v>
+        <v>4.0</v>
       </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
@@ -18071,24 +18077,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z77" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债23桐乡02本金。[23桐乡02]</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
@@ -18104,17 +18106,17 @@
       </c>
       <c r="AG77" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
+          <t>桐乡市城发控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ77" s="3" t="inlineStr">
@@ -18144,37 +18146,37 @@
       </c>
       <c r="AO77" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR77" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS77" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT77" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR77" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS77" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT77" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU77" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AV77" s="3" t="inlineStr">
@@ -18184,7 +18186,7 @@
       </c>
       <c r="AW77" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX77" s="3" t="inlineStr">
@@ -18202,7 +18204,7 @@
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26桐乡02</t>
+          <t>26皋通G1</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -18212,64 +18214,64 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>283766.SH</t>
+          <t>246017.SH</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>9.0</v>
+        <v>3.4</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>9.0</v>
+        <v>3.4</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>30.74</v>
+        <v>38.94</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>26桐乡01</t>
+          <t>24如皋交通MTN002</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2.48Y+2.00Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.7291</t>
+          <t>1.7417</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>桐乡市城发控股集团有限公司</t>
+          <t>如皋市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.97</t>
+          <t>C+ 34.53</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18293,38 +18295,38 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>4.0</v>
+        <v>5.55</v>
       </c>
       <c r="V78" s="3"/>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债23桐乡02本金。[23桐乡02]</t>
+          <t>本期公司债券募集资金扣除发行承销费用后,拟全部用于偿还到期公司债券本金。[21皋通01]</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>东吴证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
@@ -18345,74 +18347,70 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>桐乡市城发控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>如皋市交通产业集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK78" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK78" s="3"/>
       <c r="AL78" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO78" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP78" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ78" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR78" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS78" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT78" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU78" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM78" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN78" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO78" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP78" s="3" t="inlineStr">
-        <is>
-          <t>7*无效</t>
-        </is>
-      </c>
-      <c r="AQ78" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR78" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS78" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT78" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU78" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
       <c r="AV78" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -18420,7 +18418,7 @@
       </c>
       <c r="AW78" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX78" s="3" t="inlineStr">
@@ -18438,7 +18436,7 @@
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26皋通G1</t>
+          <t>26金川K3</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18448,64 +18446,64 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>246017.SH</t>
+          <t>246003.SH</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>3.4</v>
+        <v>10.0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3.4</v>
+        <v>9.0</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>38.94</v>
+        <v>34.74</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>24如皋交通MTN002</t>
+          <t>26金川MTN001</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.7417</t>
+          <t>1.8518</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>如皋市交通产业集团有限公司</t>
+          <t>金川集团股份有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.58</t>
+          <t>C 25.23</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18529,38 +18527,38 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>5.55</v>
+        <v>6.2444</v>
       </c>
       <c r="V79" s="3"/>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>甘肃省-金昌市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行承销费用后,拟全部用于偿还到期公司债券本金。[21皋通01]</t>
+          <t>本期债券募集资金拟全部用于生产性支出,包括偿还到期债务、补充流动资金、股权及基金出资等符合法律法规及监管机构允许的用途</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,首创证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
@@ -18581,7 +18579,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>如皋市交通产业集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>金川集团股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18591,10 +18589,14 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK79" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK79" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t/>
@@ -18602,7 +18604,7 @@
       </c>
       <c r="AM79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN79" s="3" t="inlineStr">
@@ -18612,32 +18614,32 @@
       </c>
       <c r="AO79" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他有色金属</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18670,7 +18672,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26金川K3</t>
+          <t>26金川K4</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18680,54 +18682,54 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>246003.SH</t>
+          <t>246048.SH</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>34.74</v>
+        <v>51.03</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26金川MTN001</t>
+          <t>26金川MTN002</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>9.97Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.8518</t>
+          <t>2.2635</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>2.2800/2.2550</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -18737,7 +18739,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C 28.09</t>
+          <t>C 25.23</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18761,7 +18763,7 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>6.2444</v>
+        <v>2.5727</v>
       </c>
       <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
@@ -18771,7 +18773,7 @@
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>2.12%~2.22%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18813,7 +18815,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>金川集团股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18823,7 +18825,7 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
+          <t>2036-09-14</t>
         </is>
       </c>
       <c r="AK80" s="3" t="inlineStr">
@@ -18906,74 +18908,74 @@
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26金川K4</t>
+          <t>26华电新能MTN001</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>246048.SH</t>
+          <t>102683601.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>51.03</v>
+        <v>27.74</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26金川MTN002</t>
+          <t>G26HX2</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>9.97Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>2.2635</t>
+          <t>1.7418</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>2.2800/2.2550</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司</t>
+          <t>华电新能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C 28.09</t>
+          <t>A- 65.98</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18983,7 +18985,7 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 10:00</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -18993,21 +18995,23 @@
       </c>
       <c r="T81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>2.5727</v>
-      </c>
-      <c r="V81" s="3"/>
+        <v>2.4667</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>2.12%~2.22%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -19018,38 +19022,38 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-金昌市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于生产性支出,包括偿还到期债务、补充流动资金、股权及基金出资等符合法律法规及监管机构允许的用途</t>
+          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,首创证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
       <c r="AE81" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF81" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG81" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
+          <t>华电新能源集团股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -19059,17 +19063,13 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2036-09-14</t>
-        </is>
-      </c>
-      <c r="AK81" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM81" s="3" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AN81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AO81" s="3" t="inlineStr">
@@ -19089,27 +19089,27 @@
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>其他有色金属</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>金属非金属新材料</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -19142,59 +19142,59 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26华电新能MTN001</t>
+          <t>26嘉科01</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>102683601.IB</t>
+          <t>283691.SH</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>27.74</v>
+        <v>44.94</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>G26HX2</t>
+          <t>25嘉科K1</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>3.78Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.7418</t>
+          <t>1.8717</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -19204,12 +19204,12 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司</t>
+          <t>浙江嘉科控股集团有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>A- 66.79</t>
+          <t>D- 1.41</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>09-10 10:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr">
@@ -19229,121 +19229,119 @@
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>2.4667</v>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>1.02</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
+          <t>本期债券的发行总额为不超过人民币6.00亿元(含6.00亿元)。扣除发行费后,募集资金计划用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF82" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG82" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司2026年度第一期中期票据</t>
+          <t>浙江嘉科控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN82" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM82" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN82" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19376,7 +19374,7 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26嘉科01</t>
+          <t>26峨旅01</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -19386,64 +19384,64 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>283691.SH</t>
+          <t>283925.SH</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>44.94</v>
+        <v>46.44</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>25嘉科K1</t>
+          <t>26峨乐旅集MTN001</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>3.78Y</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.8717</t>
+          <t>1.8487</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>浙江嘉科控股集团有限公司</t>
+          <t>四川省峨眉山乐山大佛旅游集团有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>D- 1.41</t>
+          <t>A- 60.78</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19467,17 +19465,17 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.98%~2.08%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -19488,17 +19486,17 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>四川省-乐山市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期债券的发行总额为不超过人民币6.00亿元(含6.00亿元)。扣除发行费后,募集资金计划用于偿还有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券[23峨旅01]</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信建投证券股份有限公司,平安证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
@@ -19519,7 +19517,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>浙江嘉科控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>四川省峨眉山乐山大佛旅游集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19529,7 +19527,7 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2033-09-14</t>
         </is>
       </c>
       <c r="AK83" s="3"/>
@@ -19540,7 +19538,7 @@
       </c>
       <c r="AM83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN83" s="3" t="inlineStr">
@@ -19550,37 +19548,37 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>消费者服务</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>休闲娱乐</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>休闲娱乐</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-14</t>
         </is>
       </c>
       <c r="AV83" s="3" t="inlineStr">
@@ -19590,7 +19588,7 @@
       </c>
       <c r="AW83" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX83" s="3" t="inlineStr">
@@ -19608,7 +19606,7 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26峨旅01</t>
+          <t>26苏润02</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19618,64 +19616,64 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>283925.SH</t>
+          <t>283951.SH</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.99</v>
+        <v>2.0</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>46.44</v>
+        <v>58.74</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>26峨乐旅集MTN001</t>
+          <t>26润城城投PPN001</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.8487</t>
+          <t>1.9907</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>2.0300/--</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>四川省峨眉山乐山大佛旅游集团有限公司</t>
+          <t>江苏润城城市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>A- 60.78</t>
+          <t>C+ 32.43</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19685,7 +19683,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 16:00</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -19699,19 +19697,15 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X84" s="3" t="inlineStr">
-        <is>
-          <t>1.98%~2.08%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X84" s="3"/>
       <c r="Y84" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -19720,17 +19714,17 @@
       <c r="Z84" s="3"/>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>四川省-乐山市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券[23峨旅01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金。[23苏润04]</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19751,7 +19745,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>四川省峨眉山乐山大佛旅游集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏润城城市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19761,60 +19755,52 @@
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2033-09-14</t>
-        </is>
-      </c>
-      <c r="AK84" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK84" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL84" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO84" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP84" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ84" s="3"/>
+      <c r="AR84" s="3"/>
+      <c r="AS84" s="3"/>
+      <c r="AT84" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU84" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM84" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN84" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO84" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP84" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ84" s="3" t="inlineStr">
-        <is>
-          <t>消费者服务</t>
-        </is>
-      </c>
-      <c r="AR84" s="3" t="inlineStr">
-        <is>
-          <t>休闲娱乐</t>
-        </is>
-      </c>
-      <c r="AS84" s="3" t="inlineStr">
-        <is>
-          <t>休闲娱乐</t>
-        </is>
-      </c>
-      <c r="AT84" s="3" t="inlineStr">
-        <is>
-          <t>旅游综合</t>
-        </is>
-      </c>
-      <c r="AU84" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
       <c r="AV84" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -19822,7 +19808,7 @@
       </c>
       <c r="AW84" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX84" s="3" t="inlineStr">
@@ -19840,7 +19826,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26苏润02</t>
+          <t>26嘉GT2</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19850,7 +19836,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>283951.SH</t>
+          <t>520451.SZ</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -19859,10 +19845,10 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>10.0</v>
+        <v>4.5</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>10.0</v>
+        <v>4.4</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -19870,44 +19856,44 @@
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>2.0</v>
+        <v>2.04</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>58.74</v>
+        <v>62.74</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>26润城城投PPN001</t>
+          <t>26嘉GT1</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.9907</t>
+          <t>2.0768</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>2.0300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>江苏润城城市投资控股集团有限公司</t>
+          <t>嘉兴湾北科创发展集团有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.15</t>
+          <t>D+ 9.35</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19917,7 +19903,7 @@
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>09-10 16:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
@@ -19931,15 +19917,19 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X85" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X85" s="3" t="inlineStr">
+        <is>
+          <t>2.06%~2.16%</t>
+        </is>
+      </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -19948,20 +19938,24 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金。[23苏润04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券之外的有息债务。</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD85" s="3"/>
+          <t>天风证券股份有限公司,国信证券股份有限公司,国融证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD85" s="3" t="inlineStr">
+        <is>
+          <t>浙江湾北控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE85" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -19974,12 +19968,12 @@
       </c>
       <c r="AG85" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>江苏润城城市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>嘉兴湾北科创发展集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -20004,7 +19998,7 @@
       </c>
       <c r="AM85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN85" s="3" t="inlineStr">
@@ -20014,7 +20008,7 @@
       </c>
       <c r="AO85" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP85" s="3" t="inlineStr">
@@ -20022,12 +20016,24 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AQ85" s="3"/>
-      <c r="AR85" s="3"/>
-      <c r="AS85" s="3"/>
+      <c r="AQ85" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR85" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AS85" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>计算机应用</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
@@ -20037,7 +20043,7 @@
       </c>
       <c r="AV85" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW85" s="3" t="inlineStr">
@@ -20060,7 +20066,7 @@
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26嘉GT2</t>
+          <t>26西证07</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -20070,64 +20076,64 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>520451.SZ</t>
+          <t>246054.SH</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>4.5</v>
+        <v>20.0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>4.4</v>
+        <v>18.0</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>62.74</v>
+        <v>42.94</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>26嘉GT1</t>
+          <t>26西证06</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>2.0768</t>
+          <t>1.6651</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>嘉兴湾北科创发展集团有限公司</t>
+          <t>西南证券股份有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.35</t>
+          <t>C- 17.03</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20151,48 +20157,48 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>2.73</v>
+        <v>4.32</v>
       </c>
       <c r="V86" s="3"/>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>2.06%~2.16%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z86" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z86" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券之外的有息债务。</t>
+          <t>公司本期发行募集的资金在扣除发行费用后,拟用于置换偿还到期公司债券本金的自有资金[23西证01]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,国信证券股份有限公司,国融证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD86" s="3" t="inlineStr">
-        <is>
-          <t>浙江湾北控股集团有限公司</t>
-        </is>
-      </c>
+          <t>华西证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD86" s="3"/>
       <c r="AE86" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF86" s="3" t="inlineStr">
@@ -20202,82 +20208,78 @@
       </c>
       <c r="AG86" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>嘉兴湾北科创发展集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第二期)</t>
+          <t>西南证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK86" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK86" s="3"/>
       <c r="AL86" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO86" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP86" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ86" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR86" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AS86" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="AT86" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AU86" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM86" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN86" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO86" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP86" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ86" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR86" s="3" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AS86" s="3" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AT86" s="3" t="inlineStr">
-        <is>
-          <t>计算机应用</t>
-        </is>
-      </c>
-      <c r="AU86" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV86" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW86" s="3" t="inlineStr">
@@ -20300,7 +20302,7 @@
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26西证07</t>
+          <t>西资KZ01</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20310,64 +20312,56 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>246054.SH</t>
+          <t>283852.SH</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>42.94</v>
+        <v>42.74</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>26西证06</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>2.87Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>1.6651</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>西南证券股份有限公司</t>
+          <t>西安财金资本管理有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 14.43</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20391,48 +20385,40 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X87" s="3" t="inlineStr">
-        <is>
-          <t>1.69%~1.79%</t>
-        </is>
-      </c>
-      <c r="Y87" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z87" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>公司本期发行募集的资金在扣除发行费用后,拟用于置换偿还到期公司债券本金的自有资金[23西证01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于70%的募集资金用于置换发行前一年以内合伙企业对科技创新中小微企业的股权投资、委托贷款等出资,剩余不高于30%的募集资金用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>华西证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD87" s="3"/>
+          <t>开源证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD87" s="3" t="inlineStr">
+        <is>
+          <t>西安财金投资管理有限公司</t>
+        </is>
+      </c>
       <c r="AE87" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF87" s="3" t="inlineStr">
@@ -20447,78 +20433,78 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>西南证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>西安财金资本管理有限公司2026年面向专业投资者非公开发行科技创新中小微企业支持债券</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK87" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO87" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP87" s="3"/>
+      <c r="AQ87" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR87" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS87" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT87" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU87" s="3" t="inlineStr">
+        <is>
           <t>2029-09-14</t>
         </is>
       </c>
-      <c r="AK87" s="3"/>
-      <c r="AL87" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM87" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN87" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO87" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP87" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ87" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR87" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS87" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT87" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU87" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV87" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW87" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX87" s="3" t="inlineStr">
@@ -20536,123 +20522,135 @@
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>西资KZ01</t>
+          <t>26北京农商绿色债</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>283852.SH</t>
+          <t>2621004.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>42.74</v>
+        <v>30.94</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>25北京农商科创债(柜台)</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>4.25Y</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>1.6323</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>北京农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>A- 68.47</t>
+        </is>
+      </c>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="R88" s="3" t="inlineStr">
+        <is>
+          <t>09-10 09:00</t>
+        </is>
+      </c>
+      <c r="S88" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O88" s="3" t="inlineStr">
-        <is>
-          <t>西安财金资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q88" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="R88" s="3" t="inlineStr">
-        <is>
-          <t>09-10 15:00</t>
-        </is>
-      </c>
-      <c r="S88" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T88" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="V88" s="3"/>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X88" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
+      <c r="Y88" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z88" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="AB88" s="3" t="inlineStr">
-        <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不低于70%的募集资金用于置换发行前一年以内合伙企业对科技创新中小微企业的股权投资、委托贷款等出资,剩余不高于30%的募集资金用于补充公司流动资金。</t>
-        </is>
-      </c>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB88" s="3"/>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD88" s="3" t="inlineStr">
-        <is>
-          <t>西安财金投资管理有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF88" s="3" t="inlineStr">
@@ -20662,83 +20660,83 @@
       </c>
       <c r="AG88" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>西安财金资本管理有限公司2026年面向专业投资者非公开发行科技创新中小微企业支持债券</t>
+          <t>北京农村商业银行股份有限公司2026年绿色金融债券</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK88" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK88" s="3"/>
       <c r="AL88" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AM88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO88" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP88" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ88" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR88" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS88" s="3" t="inlineStr">
+        <is>
+          <t>农商行</t>
+        </is>
+      </c>
+      <c r="AT88" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU88" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM88" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN88" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO88" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP88" s="3"/>
-      <c r="AQ88" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR88" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS88" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT88" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU88" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
       <c r="AV88" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW88" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX88" s="3" t="inlineStr">
@@ -20756,7 +20754,7 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26北京农商绿色债</t>
+          <t>26鄂联投MTN002</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -20766,64 +20764,64 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>2621004.IB</t>
+          <t>102690028.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>30.0</v>
+        <v>8.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>30.0</v>
+        <v>8.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>30.94</v>
+        <v>54.94</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>25北京农商科创债(柜台)</t>
+          <t>26联投Y4</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>4.25Y</t>
+          <t>2.80Y+N</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.6323</t>
+          <t>1.8123</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>北京农村商业银行股份有限公司</t>
+          <t>湖北省联合发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>A- 64.31</t>
+          <t>C+ 33.82</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20833,7 +20831,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -20843,21 +20841,23 @@
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V89" s="3"/>
+        <v>2.775</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W89" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X89" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y89" s="3" t="inlineStr">
@@ -20865,26 +20865,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z89" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB89" s="3"/>
+          <t>湖北省</t>
+        </is>
+      </c>
+      <c r="AB89" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为8亿元,募集资金拟全部用于偿还发行人非金融企业债务融资工具本金[23鄂联投MTN004]</t>
+        </is>
+      </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
       <c r="AE89" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF89" s="3" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>北京农村商业银行股份有限公司2026年绿色金融债券</t>
+          <t>湖北省联合发展投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
@@ -20909,53 +20909,53 @@
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK89" s="3"/>
       <c r="AL89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AO89" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU89" s="3" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="AW89" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX89" s="3" t="inlineStr">
@@ -20983,7 +20983,9 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ89" s="3"/>
+      <c r="AZ89" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
